--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R2" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,18 +748,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B3" t="n">
-        <v>79618</v>
+        <v>5493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R3" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -2370,45 +2370,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B18" t="n">
-        <v>92644</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R18" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2452,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,54 +2486,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R19" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,18 +2559,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154517</v>
+        <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>91315</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483645</v>
+        <v>483541</v>
       </c>
       <c r="R20" t="n">
-        <v>6952395</v>
+        <v>6952493</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154504</v>
+        <v>128154517</v>
       </c>
       <c r="B21" t="n">
         <v>79647</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483432</v>
+        <v>483645</v>
       </c>
       <c r="R21" t="n">
-        <v>6952552</v>
+        <v>6952395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154502</v>
+        <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>91315</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483541</v>
+        <v>483432</v>
       </c>
       <c r="R22" t="n">
-        <v>6952493</v>
+        <v>6952552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>5493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R2" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +753,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B3" t="n">
-        <v>5493</v>
+        <v>79618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R3" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B4" t="n">
-        <v>90385</v>
+        <v>79647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R4" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154527</v>
+        <v>128154525</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>90386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483615</v>
+        <v>483386</v>
       </c>
       <c r="R5" t="n">
-        <v>6952451</v>
+        <v>6952556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>91300</v>
+        <v>91301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>92640</v>
+        <v>80167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>80167</v>
+        <v>92641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,54 +2370,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92645</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R18" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,18 +2443,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,45 +2471,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B19" t="n">
-        <v>92644</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R19" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,12 +2553,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154502</v>
+        <v>128154517</v>
       </c>
       <c r="B20" t="n">
-        <v>91315</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483541</v>
+        <v>483645</v>
       </c>
       <c r="R20" t="n">
-        <v>6952493</v>
+        <v>6952395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154517</v>
+        <v>128154504</v>
       </c>
       <c r="B21" t="n">
         <v>79647</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483645</v>
+        <v>483432</v>
       </c>
       <c r="R21" t="n">
-        <v>6952395</v>
+        <v>6952552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154504</v>
+        <v>128154502</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>91316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483432</v>
+        <v>483541</v>
       </c>
       <c r="R22" t="n">
-        <v>6952552</v>
+        <v>6952493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B4" t="n">
-        <v>79647</v>
+        <v>91302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R4" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B5" t="n">
-        <v>90386</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R5" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B6" t="n">
-        <v>91301</v>
+        <v>90387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R6" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1166,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B16" t="n">
-        <v>80167</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R16" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B17" t="n">
-        <v>92641</v>
+        <v>80167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R17" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,7 +2373,7 @@
         <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>92645</v>
+        <v>92646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154517</v>
+        <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483645</v>
+        <v>483541</v>
       </c>
       <c r="R20" t="n">
-        <v>6952395</v>
+        <v>6952493</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154504</v>
+        <v>128154517</v>
       </c>
       <c r="B21" t="n">
         <v>79647</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483432</v>
+        <v>483645</v>
       </c>
       <c r="R21" t="n">
-        <v>6952552</v>
+        <v>6952395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154502</v>
+        <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>91316</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483541</v>
+        <v>483432</v>
       </c>
       <c r="R22" t="n">
-        <v>6952493</v>
+        <v>6952552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R2" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,18 +748,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B3" t="n">
-        <v>79618</v>
+        <v>5493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R3" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B4" t="n">
-        <v>91302</v>
+        <v>90387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R4" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,11 +959,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>91302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R5" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>90387</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1733,45 +1733,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,50 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>80167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>80167</v>
+        <v>92642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,45 +2370,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B18" t="n">
-        <v>92646</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R18" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2452,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,54 +2486,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92646</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R19" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,18 +2559,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154502</v>
+        <v>128154517</v>
       </c>
       <c r="B20" t="n">
-        <v>91317</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483541</v>
+        <v>483645</v>
       </c>
       <c r="R20" t="n">
-        <v>6952493</v>
+        <v>6952395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154517</v>
+        <v>128154504</v>
       </c>
       <c r="B21" t="n">
         <v>79647</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483645</v>
+        <v>483432</v>
       </c>
       <c r="R21" t="n">
-        <v>6952395</v>
+        <v>6952552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154504</v>
+        <v>128154502</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>91317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483432</v>
+        <v>483541</v>
       </c>
       <c r="R22" t="n">
-        <v>6952552</v>
+        <v>6952493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154532</v>
+        <v>128154527</v>
       </c>
       <c r="B5" t="n">
-        <v>91302</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483698</v>
+        <v>483615</v>
       </c>
       <c r="R5" t="n">
-        <v>6952332</v>
+        <v>6952451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>91302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R6" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1161,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -1733,50 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R12" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R13" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,6 +1928,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -1733,45 +1733,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,50 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>91302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R5" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154532</v>
+        <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>91302</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483698</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6952332</v>
+        <v>6952451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1166,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154532</v>
+        <v>128154527</v>
       </c>
       <c r="B5" t="n">
-        <v>91302</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483698</v>
+        <v>483615</v>
       </c>
       <c r="R5" t="n">
-        <v>6952332</v>
+        <v>6952451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>91302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R6" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1161,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1733,50 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>92642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R12" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R13" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,6 +1928,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>5493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R2" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +753,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B3" t="n">
-        <v>5493</v>
+        <v>79621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R3" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154525</v>
+        <v>128154532</v>
       </c>
       <c r="B4" t="n">
-        <v>90387</v>
+        <v>91310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483386</v>
+        <v>483698</v>
       </c>
       <c r="R4" t="n">
-        <v>6952556</v>
+        <v>6952332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154527</v>
+        <v>128154525</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>90393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483615</v>
+        <v>483386</v>
       </c>
       <c r="R5" t="n">
-        <v>6952451</v>
+        <v>6952556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154532</v>
+        <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>91302</v>
+        <v>79650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483698</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6952332</v>
+        <v>6952451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1166,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1199,7 @@
         <v>128154505</v>
       </c>
       <c r="B7" t="n">
-        <v>81004</v>
+        <v>81007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>80167</v>
+        <v>80170</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,54 +2370,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R18" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,18 +2443,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,45 +2471,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B19" t="n">
-        <v>92646</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R19" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,12 +2553,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154517</v>
+        <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>91325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483645</v>
+        <v>483541</v>
       </c>
       <c r="R20" t="n">
-        <v>6952395</v>
+        <v>6952493</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154504</v>
+        <v>128154517</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483432</v>
+        <v>483645</v>
       </c>
       <c r="R21" t="n">
-        <v>6952552</v>
+        <v>6952395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154502</v>
+        <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>91317</v>
+        <v>79650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483541</v>
+        <v>483432</v>
       </c>
       <c r="R22" t="n">
-        <v>6952493</v>
+        <v>6952552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2893,7 @@
         <v>128154520</v>
       </c>
       <c r="B23" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91613</v>
+        <v>91621</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>128154547</v>
       </c>
       <c r="B26" t="n">
-        <v>80036</v>
+        <v>80039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128154526</v>
       </c>
       <c r="B3" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>128154532</v>
       </c>
       <c r="B4" t="n">
-        <v>91310</v>
+        <v>91402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128154525</v>
       </c>
       <c r="B5" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128154505</v>
       </c>
       <c r="B7" t="n">
-        <v>81007</v>
+        <v>81068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,45 +2370,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B18" t="n">
-        <v>92654</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R18" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2452,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,54 +2486,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92746</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R19" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,18 +2559,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154502</v>
+        <v>128154517</v>
       </c>
       <c r="B20" t="n">
-        <v>91325</v>
+        <v>79702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483541</v>
+        <v>483645</v>
       </c>
       <c r="R20" t="n">
-        <v>6952493</v>
+        <v>6952395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154517</v>
+        <v>128154504</v>
       </c>
       <c r="B21" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483645</v>
+        <v>483432</v>
       </c>
       <c r="R21" t="n">
-        <v>6952395</v>
+        <v>6952552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154504</v>
+        <v>128154502</v>
       </c>
       <c r="B22" t="n">
-        <v>79650</v>
+        <v>91417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483432</v>
+        <v>483541</v>
       </c>
       <c r="R22" t="n">
-        <v>6952552</v>
+        <v>6952493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2893,7 @@
         <v>128154520</v>
       </c>
       <c r="B23" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91621</v>
+        <v>91713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91595</v>
+        <v>91687</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>128154547</v>
       </c>
       <c r="B26" t="n">
-        <v>80039</v>
+        <v>80092</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B4" t="n">
-        <v>91402</v>
+        <v>90485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R4" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,11 +961,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154525</v>
+        <v>128154532</v>
       </c>
       <c r="B5" t="n">
-        <v>90485</v>
+        <v>91402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483386</v>
+        <v>483698</v>
       </c>
       <c r="R5" t="n">
-        <v>6952556</v>
+        <v>6952332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1060,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1733,45 +1733,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>5493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,50 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,54 +2370,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92746</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R18" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,18 +2443,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2475,7 +2460,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2486,45 +2471,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B19" t="n">
-        <v>92746</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R19" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,12 +2553,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B4" t="n">
-        <v>90485</v>
+        <v>79702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R4" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154527</v>
+        <v>128154525</v>
       </c>
       <c r="B6" t="n">
-        <v>79702</v>
+        <v>90485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483615</v>
+        <v>483386</v>
       </c>
       <c r="R6" t="n">
-        <v>6952451</v>
+        <v>6952556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1733,50 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R12" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R13" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,6 +1928,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B16" t="n">
-        <v>80223</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R16" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R17" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154517</v>
+        <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>79702</v>
+        <v>91417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483645</v>
+        <v>483541</v>
       </c>
       <c r="R20" t="n">
-        <v>6952395</v>
+        <v>6952493</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154504</v>
+        <v>128154517</v>
       </c>
       <c r="B21" t="n">
         <v>79702</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483432</v>
+        <v>483645</v>
       </c>
       <c r="R21" t="n">
-        <v>6952552</v>
+        <v>6952395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154502</v>
+        <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>91417</v>
+        <v>79702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483541</v>
+        <v>483432</v>
       </c>
       <c r="R22" t="n">
-        <v>6952493</v>
+        <v>6952552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>80223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>128154526</v>
       </c>
       <c r="B3" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154527</v>
+        <v>128154525</v>
       </c>
       <c r="B4" t="n">
-        <v>79702</v>
+        <v>90497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483615</v>
+        <v>483386</v>
       </c>
       <c r="R4" t="n">
-        <v>6952451</v>
+        <v>6952556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
         <v>128154532</v>
       </c>
       <c r="B5" t="n">
-        <v>91402</v>
+        <v>91414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>90485</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1199,7 @@
         <v>128154505</v>
       </c>
       <c r="B7" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,45 +1733,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>5493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,50 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B16" t="n">
-        <v>80223</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R16" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>80227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R17" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,7 +2373,7 @@
         <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>92746</v>
+        <v>92758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>128154517</v>
       </c>
       <c r="B21" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>128154520</v>
       </c>
       <c r="B23" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91713</v>
+        <v>91725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91687</v>
+        <v>91699</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>128154547</v>
       </c>
       <c r="B26" t="n">
-        <v>80092</v>
+        <v>80096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>79677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R2" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,18 +748,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B3" t="n">
-        <v>79677</v>
+        <v>5493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R3" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +854,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154532</v>
+        <v>128154527</v>
       </c>
       <c r="B5" t="n">
-        <v>91414</v>
+        <v>79706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483698</v>
+        <v>483615</v>
       </c>
       <c r="R5" t="n">
-        <v>6952332</v>
+        <v>6952451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>91414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R6" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1161,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154502</v>
+        <v>128154517</v>
       </c>
       <c r="B20" t="n">
-        <v>91429</v>
+        <v>79706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483541</v>
+        <v>483645</v>
       </c>
       <c r="R20" t="n">
-        <v>6952493</v>
+        <v>6952395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154517</v>
+        <v>128154504</v>
       </c>
       <c r="B21" t="n">
         <v>79706</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483645</v>
+        <v>483432</v>
       </c>
       <c r="R21" t="n">
-        <v>6952395</v>
+        <v>6952552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154504</v>
+        <v>128154502</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>91429</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483432</v>
+        <v>483541</v>
       </c>
       <c r="R22" t="n">
-        <v>6952552</v>
+        <v>6952493</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154526</v>
+        <v>128154501</v>
       </c>
       <c r="B2" t="n">
-        <v>79677</v>
+        <v>5493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483615</v>
+        <v>483569</v>
       </c>
       <c r="R2" t="n">
-        <v>6952451</v>
+        <v>6952286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +753,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -776,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154501</v>
+        <v>128154526</v>
       </c>
       <c r="B3" t="n">
-        <v>5493</v>
+        <v>79679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483569</v>
+        <v>483615</v>
       </c>
       <c r="R3" t="n">
-        <v>6952286</v>
+        <v>6952451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,18 +860,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +891,7 @@
         <v>128154525</v>
       </c>
       <c r="B4" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>128154527</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>91414</v>
+        <v>91416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128154505</v>
       </c>
       <c r="B7" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,50 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>92756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R12" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R13" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,6 +1928,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>80227</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,45 +2370,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B18" t="n">
-        <v>92758</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R18" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2452,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2471,54 +2486,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>92760</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R19" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2553,18 +2559,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>128154517</v>
       </c>
       <c r="B20" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>128154504</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>128154502</v>
       </c>
       <c r="B22" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>128154520</v>
       </c>
       <c r="B23" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91699</v>
+        <v>91701</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>128154547</v>
       </c>
       <c r="B26" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154525</v>
+        <v>128154532</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>91416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483386</v>
+        <v>483698</v>
       </c>
       <c r="R4" t="n">
-        <v>6952556</v>
+        <v>6952332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1090,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B6" t="n">
-        <v>91416</v>
+        <v>90499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R6" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1166,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1733,45 +1733,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B12" t="n">
-        <v>92756</v>
+        <v>5493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1839,50 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1929,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R16" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R17" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2370,54 +2370,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154507</v>
+        <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>92760</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483548</v>
+        <v>483241</v>
       </c>
       <c r="R18" t="n">
-        <v>6952491</v>
+        <v>6952425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,18 +2443,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Gammalt gnag.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2486,45 +2471,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154542</v>
+        <v>128154507</v>
       </c>
       <c r="B19" t="n">
-        <v>92760</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483241</v>
+        <v>483548</v>
       </c>
       <c r="R19" t="n">
-        <v>6952425</v>
+        <v>6952491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,12 +2553,18 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2587,32 +2587,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154517</v>
+        <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>91431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483645</v>
+        <v>483541</v>
       </c>
       <c r="R20" t="n">
-        <v>6952395</v>
+        <v>6952493</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154504</v>
+        <v>128154517</v>
       </c>
       <c r="B21" t="n">
         <v>79708</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483432</v>
+        <v>483645</v>
       </c>
       <c r="R21" t="n">
-        <v>6952552</v>
+        <v>6952395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,32 +2789,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154502</v>
+        <v>128154504</v>
       </c>
       <c r="B22" t="n">
-        <v>91431</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483541</v>
+        <v>483432</v>
       </c>
       <c r="R22" t="n">
-        <v>6952493</v>
+        <v>6952552</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -877,7 +877,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B4" t="n">
-        <v>91416</v>
+        <v>90499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R4" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,11 +961,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -983,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>91417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R5" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B6" t="n">
-        <v>90499</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1300,7 +1300,7 @@
         <v>128154503</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1630,7 +1630,7 @@
         <v>128154494</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,50 +1733,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154535</v>
+        <v>128154506</v>
       </c>
       <c r="B12" t="n">
-        <v>5493</v>
+        <v>92757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483498</v>
+        <v>483410</v>
       </c>
       <c r="R12" t="n">
-        <v>6952339</v>
+        <v>6952352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1808,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1834,7 +1828,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1845,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154506</v>
+        <v>128154535</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>5493</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483410</v>
+        <v>483498</v>
       </c>
       <c r="R13" t="n">
-        <v>6952352</v>
+        <v>6952339</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,6 +1928,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1954,7 +1954,7 @@
         <v>128154550</v>
       </c>
       <c r="B14" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128154522</v>
       </c>
       <c r="B15" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2373,7 +2373,7 @@
         <v>128154542</v>
       </c>
       <c r="B18" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2590,7 +2590,7 @@
         <v>128154502</v>
       </c>
       <c r="B20" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2994,7 +2994,7 @@
         <v>128154543</v>
       </c>
       <c r="B24" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3095,7 +3095,7 @@
         <v>128154509</v>
       </c>
       <c r="B25" t="n">
-        <v>91701</v>
+        <v>91702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Staaf, Pär Hedberg</t>
+          <t>Pär Hedberg, Johan Staaf</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154525</v>
+        <v>128154527</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>79708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483386</v>
+        <v>483615</v>
       </c>
       <c r="R4" t="n">
-        <v>6952556</v>
+        <v>6952451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154532</v>
+        <v>128154525</v>
       </c>
       <c r="B5" t="n">
-        <v>91417</v>
+        <v>90499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483698</v>
+        <v>483386</v>
       </c>
       <c r="R5" t="n">
-        <v>6952332</v>
+        <v>6952556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1090,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154527</v>
+        <v>128154532</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>91417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,21 +1101,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1130,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R6" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1161,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154508</v>
+        <v>128154519</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483734</v>
+        <v>483564</v>
       </c>
       <c r="R16" t="n">
-        <v>6952352</v>
+        <v>6952460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,10 +2264,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154519</v>
+        <v>128154508</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483564</v>
+        <v>483734</v>
       </c>
       <c r="R17" t="n">
-        <v>6952460</v>
+        <v>6952352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Förra årets fruktkroppar.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128154501</v>
+        <v>128154543</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483569</v>
+        <v>483241</v>
       </c>
       <c r="R2" t="n">
-        <v>6952286</v>
+        <v>6952425</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,18 +748,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128154526</v>
+        <v>128154532</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483615</v>
+        <v>483698</v>
       </c>
       <c r="R3" t="n">
-        <v>6952451</v>
+        <v>6952332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +849,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov kolad tallåga.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,7 +871,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -888,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128154527</v>
+        <v>128154497</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483615</v>
+        <v>483064</v>
       </c>
       <c r="R4" t="n">
-        <v>6952451</v>
+        <v>6952746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +972,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154525</v>
+        <v>128154499</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483386</v>
+        <v>483359</v>
       </c>
       <c r="R5" t="n">
-        <v>6952556</v>
+        <v>6952314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1073,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1090,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128154532</v>
+        <v>128154512</v>
       </c>
       <c r="B6" t="n">
-        <v>91417</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1101,21 +1095,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483698</v>
+        <v>483046</v>
       </c>
       <c r="R6" t="n">
-        <v>6952332</v>
+        <v>6952740</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,11 +1157,6 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov kolad tallåga.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1185,7 +1174,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1196,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128154505</v>
+        <v>128154520</v>
       </c>
       <c r="B7" t="n">
-        <v>81074</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483432</v>
+        <v>483512</v>
       </c>
       <c r="R7" t="n">
-        <v>6952552</v>
+        <v>6952240</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1275,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1297,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128154503</v>
+        <v>128154545</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483616</v>
+        <v>483333</v>
       </c>
       <c r="R8" t="n">
-        <v>6952412</v>
+        <v>6952317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1357,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128154511</v>
+        <v>128154495</v>
       </c>
       <c r="B9" t="n">
-        <v>5493</v>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,39 +1398,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101410</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483587</v>
+        <v>483064</v>
       </c>
       <c r="R9" t="n">
-        <v>6952228</v>
+        <v>6952746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,18 +1460,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1504,7 +1477,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1515,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128154523</v>
+        <v>128154505</v>
       </c>
       <c r="B10" t="n">
-        <v>5493</v>
+        <v>81312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,39 +1499,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483392</v>
+        <v>483432</v>
       </c>
       <c r="R10" t="n">
-        <v>6952332</v>
+        <v>6952552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,18 +1561,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1616,7 +1578,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1627,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128154494</v>
+        <v>128154514</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483613</v>
+        <v>483046</v>
       </c>
       <c r="R11" t="n">
-        <v>6952463</v>
+        <v>6952740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,45 +1690,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128154506</v>
+        <v>128154509</v>
       </c>
       <c r="B12" t="n">
-        <v>92757</v>
+        <v>92157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1102</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483410</v>
+        <v>483494</v>
       </c>
       <c r="R12" t="n">
-        <v>6952352</v>
+        <v>6952529</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,17 +1766,13 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1828,7 +1784,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1839,10 +1795,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128154535</v>
+        <v>128154525</v>
       </c>
       <c r="B13" t="n">
-        <v>5493</v>
+        <v>90932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,39 +1806,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101410</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483498</v>
+        <v>483386</v>
       </c>
       <c r="R13" t="n">
-        <v>6952339</v>
+        <v>6952556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,18 +1868,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1940,7 +1885,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1951,32 +1896,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128154550</v>
+        <v>128154522</v>
       </c>
       <c r="B14" t="n">
-        <v>92757</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1986,10 +1931,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483627</v>
+        <v>483601</v>
       </c>
       <c r="R14" t="n">
-        <v>6952417</v>
+        <v>6952475</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,11 +1967,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,10 +1997,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128154522</v>
+        <v>128154496</v>
       </c>
       <c r="B15" t="n">
-        <v>92950</v>
+        <v>91831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,21 +2008,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2032,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483601</v>
+        <v>483064</v>
       </c>
       <c r="R15" t="n">
-        <v>6952475</v>
+        <v>6952746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2147,7 +2087,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2158,14 +2098,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128154519</v>
+        <v>128154494</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2193,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483564</v>
+        <v>483613</v>
       </c>
       <c r="R16" t="n">
-        <v>6952460</v>
+        <v>6952463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2193,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2264,32 +2204,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128154508</v>
+        <v>128154503</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2239,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483734</v>
+        <v>483616</v>
       </c>
       <c r="R17" t="n">
-        <v>6952352</v>
+        <v>6952412</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,7 +2279,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,7 +2299,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2370,32 +2310,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128154542</v>
+        <v>128154506</v>
       </c>
       <c r="B18" t="n">
-        <v>92761</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2405,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483241</v>
+        <v>483410</v>
       </c>
       <c r="R18" t="n">
-        <v>6952425</v>
+        <v>6952352</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2383,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2460,7 +2405,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2471,54 +2416,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128154507</v>
+        <v>128154515</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483548</v>
+        <v>483068</v>
       </c>
       <c r="R19" t="n">
-        <v>6952491</v>
+        <v>6952781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,7 +2491,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Gammalt gnag.</t>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,7 +2500,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2576,7 +2511,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2587,32 +2522,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128154502</v>
+        <v>128154519</v>
       </c>
       <c r="B20" t="n">
-        <v>91432</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2622,10 +2557,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483541</v>
+        <v>483564</v>
       </c>
       <c r="R20" t="n">
-        <v>6952493</v>
+        <v>6952460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,6 +2593,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128154517</v>
+        <v>128154550</v>
       </c>
       <c r="B21" t="n">
-        <v>79708</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2639,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483645</v>
+        <v>483627</v>
       </c>
       <c r="R21" t="n">
-        <v>6952395</v>
+        <v>6952417</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,6 +2701,11 @@
           <t>2025-04-25</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Förra årets fruktkroppar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2778,7 +2723,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2789,32 +2734,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128154504</v>
+        <v>128154542</v>
       </c>
       <c r="B22" t="n">
-        <v>79708</v>
+        <v>93201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483432</v>
+        <v>483241</v>
       </c>
       <c r="R22" t="n">
-        <v>6952552</v>
+        <v>6952425</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,32 +2835,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128154520</v>
+        <v>128154502</v>
       </c>
       <c r="B23" t="n">
-        <v>78755</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2925,10 +2870,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483512</v>
+        <v>483541</v>
       </c>
       <c r="R23" t="n">
-        <v>6952240</v>
+        <v>6952493</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2925,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2991,32 +2936,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128154543</v>
+        <v>128154528</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>78730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3026,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483241</v>
+        <v>483336</v>
       </c>
       <c r="R24" t="n">
-        <v>6952425</v>
+        <v>6952321</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3026,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3092,10 +3037,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128154509</v>
+        <v>128154504</v>
       </c>
       <c r="B25" t="n">
-        <v>91702</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3103,37 +3048,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1102</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483494</v>
+        <v>483432</v>
       </c>
       <c r="R25" t="n">
-        <v>6952529</v>
+        <v>6952552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,9 +3114,8 @@
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3186,7 +3127,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3197,32 +3138,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128154547</v>
+        <v>128154517</v>
       </c>
       <c r="B26" t="n">
-        <v>80098</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3232,10 +3173,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483694</v>
+        <v>483645</v>
       </c>
       <c r="R26" t="n">
-        <v>6952331</v>
+        <v>6952395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,7 +3228,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3298,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128154544</v>
+        <v>128154527</v>
       </c>
       <c r="B27" t="n">
-        <v>5493</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,39 +3250,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Näktesbergen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483425</v>
+        <v>483615</v>
       </c>
       <c r="R27" t="n">
-        <v>6952395</v>
+        <v>6952451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,18 +3312,12 @@
           <t>2025-04-25</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3399,10 +3329,1861 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Pär Hedberg, Johan Staaf</t>
+          <t>Johan Staaf, Pär Hedberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128154547</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483694</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6952331</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128154508</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483734</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6952352</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128154538</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483066</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6952764</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128154501</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483569</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6952286</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128154511</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483587</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6952228</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128154521</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483508</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6952220</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128154523</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483392</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6952332</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128154533</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483064</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6952564</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128154535</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483498</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6952339</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128154544</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>483425</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6952395</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128154551</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>483036</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6952734</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128154552</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483041</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6952742</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla gnag på död tall.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128154553</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483215</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6952792</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128154507</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>483548</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6952491</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gammalt gnag.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128154513</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>483046</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6952740</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128154526</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6952451</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128154529</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Näktesbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>483336</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6952321</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Johan Staaf, Pär Hedberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>

--- a/artfynd/A 7488-2023 artfynd.xlsx
+++ b/artfynd/A 7488-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154497</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154520</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154545</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154495</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154514</t>
         </is>
       </c>
     </row>
@@ -1792,6 +1847,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154525</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154522</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154496</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154494</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2413,6 +2498,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154515</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2625,6 +2720,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154519</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154550</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2832,6 +2937,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154542</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2933,6 +3043,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154502</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3034,6 +3149,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154528</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154504</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3236,6 +3361,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154517</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3337,6 +3467,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154527</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3438,6 +3573,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154547</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3544,6 +3684,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154508</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3643,6 +3788,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154538</t>
         </is>
       </c>
     </row>
@@ -3757,6 +3907,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154501</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3869,6 +4024,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154511</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3981,6 +4141,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154521</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4093,6 +4258,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154523</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4205,6 +4375,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154533</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4317,6 +4492,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154535</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4429,6 +4609,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154544</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4541,6 +4726,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154551</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4655,6 +4845,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154552</t>
         </is>
       </c>
     </row>
@@ -4769,6 +4964,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154553</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4885,6 +5085,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154507</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4986,6 +5191,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154513</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5087,6 +5297,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154526</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5188,8 +5403,58 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>